--- a/data/split/ITWL_Grajewo19_cut_small/ITWL_Grajewo19_cut_small.xlsx
+++ b/data/split/ITWL_Grajewo19_cut_small/ITWL_Grajewo19_cut_small.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Tree Labels" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Species Reference" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Available labels lookup" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
